--- a/output/paket/04_BÜTÇE VE HAKEDİŞ/Gym_Maltepe_HAKEDİŞ ŞABLONU.xlsx
+++ b/output/paket/04_BÜTÇE VE HAKEDİŞ/Gym_Maltepe_HAKEDİŞ ŞABLONU.xlsx
@@ -1110,7 +1110,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev E · Sarı sütunlar her hakediş döneminde doldurulur</t>
+          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev F · Sarı sütunlar her hakediş döneminde doldurulur</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       <c r="C15" s="20" t="n"/>
       <c r="D15" s="21" t="inlineStr">
         <is>
-          <t>514.423 – 866.708</t>
+          <t>540.728 – 909.501</t>
         </is>
       </c>
       <c r="E15" s="22" t="n"/>
@@ -1582,7 +1582,7 @@
       <c r="C16" s="20" t="n"/>
       <c r="D16" s="27" t="inlineStr">
         <is>
-          <t>402.580 – 682.600</t>
+          <t>412.220 – 698.140</t>
         </is>
       </c>
       <c r="E16" s="22" t="n"/>

--- a/output/paket/04_BÜTÇE VE HAKEDİŞ/Gym_Maltepe_HAKEDİŞ ŞABLONU.xlsx
+++ b/output/paket/04_BÜTÇE VE HAKEDİŞ/Gym_Maltepe_HAKEDİŞ ŞABLONU.xlsx
@@ -1110,7 +1110,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev F · Sarı sütunlar her hakediş döneminde doldurulur</t>
+          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev G · Sarı sütunlar her hakediş döneminde doldurulur</t>
         </is>
       </c>
     </row>

--- a/output/paket/04_BÜTÇE VE HAKEDİŞ/Gym_Maltepe_HAKEDİŞ ŞABLONU.xlsx
+++ b/output/paket/04_BÜTÇE VE HAKEDİŞ/Gym_Maltepe_HAKEDİŞ ŞABLONU.xlsx
@@ -1110,7 +1110,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev G · Sarı sütunlar her hakediş döneminde doldurulur</t>
+          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev H · Sarı sütunlar her hakediş döneminde doldurulur</t>
         </is>
       </c>
     </row>

--- a/output/paket/04_BÜTÇE VE HAKEDİŞ/Gym_Maltepe_HAKEDİŞ ŞABLONU.xlsx
+++ b/output/paket/04_BÜTÇE VE HAKEDİŞ/Gym_Maltepe_HAKEDİŞ ŞABLONU.xlsx
@@ -1186,7 +1186,7 @@
       <c r="C5" s="20" t="n"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t>155.794 – 247.876</t>
+          <t>155.584 – 247.578</t>
         </is>
       </c>
       <c r="E5" s="22" t="n"/>
@@ -1222,7 +1222,7 @@
       <c r="C6" s="20" t="n"/>
       <c r="D6" s="27" t="inlineStr">
         <is>
-          <t>354.543 – 450.588</t>
+          <t>347.976 – 442.263</t>
         </is>
       </c>
       <c r="E6" s="22" t="n"/>
@@ -1258,7 +1258,7 @@
       <c r="C7" s="20" t="n"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t>86.050 – 122.188</t>
+          <t>85.690 – 121.692</t>
         </is>
       </c>
       <c r="E7" s="22" t="n"/>
@@ -1294,7 +1294,7 @@
       <c r="C8" s="20" t="n"/>
       <c r="D8" s="27" t="inlineStr">
         <is>
-          <t>254.653 – 377.585</t>
+          <t>260.316 – 386.458</t>
         </is>
       </c>
       <c r="E8" s="22" t="n"/>
@@ -1330,7 +1330,7 @@
       <c r="C9" s="20" t="n"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t>102.629 – 152.964</t>
+          <t>99.653 – 148.560</t>
         </is>
       </c>
       <c r="E9" s="22" t="n"/>
@@ -1366,7 +1366,7 @@
       <c r="C10" s="20" t="n"/>
       <c r="D10" s="27" t="inlineStr">
         <is>
-          <t>309.829 – 466.315</t>
+          <t>328.251 – 495.718</t>
         </is>
       </c>
       <c r="E10" s="22" t="n"/>
@@ -1546,7 +1546,7 @@
       <c r="C15" s="20" t="n"/>
       <c r="D15" s="21" t="inlineStr">
         <is>
-          <t>540.728 – 909.501</t>
+          <t>539.693 – 907.712</t>
         </is>
       </c>
       <c r="E15" s="22" t="n"/>
@@ -1582,7 +1582,7 @@
       <c r="C16" s="20" t="n"/>
       <c r="D16" s="27" t="inlineStr">
         <is>
-          <t>412.220 – 698.140</t>
+          <t>412.340 – 698.350</t>
         </is>
       </c>
       <c r="E16" s="22" t="n"/>
@@ -1916,7 +1916,7 @@
         </is>
       </c>
       <c r="D8" s="41" t="n">
-        <v>6.19</v>
+        <v>5.84</v>
       </c>
       <c r="E8" s="42" t="n"/>
       <c r="F8" s="43">
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="D14" s="41" t="n">
-        <v>60.42</v>
+        <v>58.57</v>
       </c>
       <c r="E14" s="42" t="n"/>
       <c r="F14" s="43">
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="D17" s="51" t="n">
-        <v>31.76</v>
+        <v>31.94</v>
       </c>
       <c r="E17" s="42" t="n"/>
       <c r="F17" s="52">
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="D18" s="41" t="n">
-        <v>22.31</v>
+        <v>22.34</v>
       </c>
       <c r="E18" s="42" t="n"/>
       <c r="F18" s="43">
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="D19" s="51" t="n">
-        <v>32.98</v>
+        <v>32.77</v>
       </c>
       <c r="E19" s="42" t="n"/>
       <c r="F19" s="52">
@@ -2348,7 +2348,7 @@
         </is>
       </c>
       <c r="D20" s="41" t="n">
-        <v>10.07</v>
+        <v>10.21</v>
       </c>
       <c r="E20" s="42" t="n"/>
       <c r="F20" s="43">
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="D21" s="51" t="n">
-        <v>6.19</v>
+        <v>5.84</v>
       </c>
       <c r="E21" s="42" t="n"/>
       <c r="F21" s="52">
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="D23" s="51" t="n">
-        <v>31.76</v>
+        <v>31.94</v>
       </c>
       <c r="E23" s="42" t="n"/>
       <c r="F23" s="52">
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="D24" s="41" t="n">
-        <v>22.31</v>
+        <v>22.34</v>
       </c>
       <c r="E24" s="42" t="n"/>
       <c r="F24" s="43">
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="D25" s="51" t="n">
-        <v>32.98</v>
+        <v>32.77</v>
       </c>
       <c r="E25" s="42" t="n"/>
       <c r="F25" s="52">
@@ -2564,7 +2564,7 @@
         </is>
       </c>
       <c r="D26" s="41" t="n">
-        <v>6.19</v>
+        <v>5.84</v>
       </c>
       <c r="E26" s="42" t="n"/>
       <c r="F26" s="43">
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="D27" s="51" t="n">
-        <v>10.07</v>
+        <v>10.21</v>
       </c>
       <c r="E27" s="42" t="n"/>
       <c r="F27" s="52">
@@ -2642,7 +2642,7 @@
         </is>
       </c>
       <c r="D28" s="41" t="n">
-        <v>31.76</v>
+        <v>31.94</v>
       </c>
       <c r="E28" s="42" t="n"/>
       <c r="F28" s="43">
@@ -2681,7 +2681,7 @@
         </is>
       </c>
       <c r="D29" s="51" t="n">
-        <v>40.62</v>
+        <v>55.41</v>
       </c>
       <c r="E29" s="42" t="n"/>
       <c r="F29" s="52">
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="D30" s="41" t="n">
-        <v>23.65</v>
+        <v>24.39</v>
       </c>
       <c r="E30" s="42" t="n"/>
       <c r="F30" s="43">
@@ -2759,7 +2759,7 @@
         </is>
       </c>
       <c r="D31" s="51" t="n">
-        <v>16.17</v>
+        <v>16.52</v>
       </c>
       <c r="E31" s="42" t="n"/>
       <c r="F31" s="52">
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="D33" s="51" t="n">
-        <v>21.68</v>
+        <v>21.08</v>
       </c>
       <c r="E33" s="42" t="n"/>
       <c r="F33" s="52">
@@ -2858,7 +2858,7 @@
         </is>
       </c>
       <c r="D34" s="41" t="n">
-        <v>14.46</v>
+        <v>13.94</v>
       </c>
       <c r="E34" s="42" t="n"/>
       <c r="F34" s="43">
@@ -2897,7 +2897,7 @@
         </is>
       </c>
       <c r="D35" s="51" t="n">
-        <v>6.19</v>
+        <v>5.84</v>
       </c>
       <c r="E35" s="42" t="n"/>
       <c r="F35" s="52">
@@ -2936,7 +2936,7 @@
         </is>
       </c>
       <c r="D36" s="41" t="n">
-        <v>23.47</v>
+        <v>22.87</v>
       </c>
       <c r="E36" s="42" t="n"/>
       <c r="F36" s="43">
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="D37" s="51" t="n">
-        <v>52.61</v>
+        <v>52.03</v>
       </c>
       <c r="E37" s="42" t="n"/>
       <c r="F37" s="52">
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="D39" s="51" t="n">
-        <v>32.98</v>
+        <v>32.77</v>
       </c>
       <c r="E39" s="42" t="n"/>
       <c r="F39" s="52">
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="D40" s="41" t="n">
-        <v>10.07</v>
+        <v>10.21</v>
       </c>
       <c r="E40" s="42" t="n"/>
       <c r="F40" s="43">
@@ -3113,7 +3113,7 @@
         </is>
       </c>
       <c r="D41" s="51" t="n">
-        <v>6.19</v>
+        <v>5.84</v>
       </c>
       <c r="E41" s="42" t="n"/>
       <c r="F41" s="52">
@@ -3152,7 +3152,7 @@
         </is>
       </c>
       <c r="D42" s="41" t="n">
-        <v>54.07</v>
+        <v>54.28</v>
       </c>
       <c r="E42" s="42" t="n"/>
       <c r="F42" s="43">
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="D45" s="51" t="n">
-        <v>286.08</v>
+        <v>336.35</v>
       </c>
       <c r="E45" s="42" t="n"/>
       <c r="F45" s="52">
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="D46" s="41" t="n">
-        <v>8.35</v>
+        <v>8.09</v>
       </c>
       <c r="E46" s="42" t="n"/>
       <c r="F46" s="43">
@@ -3347,7 +3347,7 @@
         </is>
       </c>
       <c r="D47" s="51" t="n">
-        <v>43.05</v>
+        <v>42.98</v>
       </c>
       <c r="E47" s="42" t="n"/>
       <c r="F47" s="52">

--- a/output/paket/04_BÜTÇE VE HAKEDİŞ/Gym_Maltepe_HAKEDİŞ ŞABLONU.xlsx
+++ b/output/paket/04_BÜTÇE VE HAKEDİŞ/Gym_Maltepe_HAKEDİŞ ŞABLONU.xlsx
@@ -1546,7 +1546,7 @@
       <c r="C15" s="20" t="n"/>
       <c r="D15" s="21" t="inlineStr">
         <is>
-          <t>539.693 – 907.712</t>
+          <t>537.495 – 904.040</t>
         </is>
       </c>
       <c r="E15" s="22" t="n"/>
